--- a/education_forms/018_ai_grading_pilot_participation_consent_form--education_forms.xlsx
+++ b/education_forms/018_ai_grading_pilot_participation_consent_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -971,12 +971,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'undergraduate_student',_'value':_'undergrad'}</t>
+          <t>undergraduate_student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Undergraduate Student', 'value': 'undergrad'}</t>
+          <t>Undergraduate Student</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'graduate_student',_'value':_'grad'}</t>
+          <t>graduate_student</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Graduate Student', 'value': 'grad'}</t>
+          <t>Graduate Student</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'faculty_/_instructor',_'value':_'faculty'}</t>
+          <t>faculty_/_instructor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Faculty / Instructor', 'value': 'faculty'}</t>
+          <t>Faculty / Instructor</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'teaching_assistant_(ta)',_'value':_'ta'}</t>
+          <t>teaching_assistant_(ta)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Teaching Assistant (TA)', 'value': 'ta'}</t>
+          <t>Teaching Assistant (TA)</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_have_read_it',_'value':_true}</t>
+          <t>yes,_i_have_read_it</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I have read it', 'value': True}</t>
+          <t>Yes, I have read it</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_need_a_copy',_'value':_'request_copy'}</t>
+          <t>no,_i_need_a_copy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No, I need a copy', 'value': 'request_copy'}</t>
+          <t>No, I need a copy</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent_to_participate',_'value':_true}</t>
+          <t>yes,_i_consent_to_participate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent to participate', 'value': True}</t>
+          <t>Yes, I consent to participate</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_wish_to_participate',_'value':_false}</t>
+          <t>no,_i_do_not_wish_to_participate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not wish to participate', 'value': False}</t>
+          <t>No, I do not wish to participate</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_consent',_'value':_true}</t>
+          <t>yes,_i_consent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I consent', 'value': True}</t>
+          <t>Yes, I consent</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_consent',_'value':_false}</t>
+          <t>no,_i_do_not_consent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not consent', 'value': False}</t>
+          <t>No, I do not consent</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'complete_anonymization_(no_identifying_links)',_'value':_'complete'}</t>
+          <t>complete_anonymization_(no_identifying_links)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Complete Anonymization (No identifying links)', 'value': 'complete'}</t>
+          <t>Complete Anonymization (No identifying links)</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'linked_pseudonymization_(allows_withdrawal_of_data_later)',_'value':_'linked'}</t>
+          <t>linked_pseudonymization_(allows_withdrawal_of_data_later)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Linked Pseudonymization (Allows withdrawal of data later)', 'value': 'linked'}</t>
+          <t>Linked Pseudonymization (Allows withdrawal of data later)</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_i_can_withdraw_from_the_pilot_at_any_time_without_academic_penalty.',_'value':_'acknowledged'}</t>
+          <t>i_understand_i_can_withdraw_from_the_pilot_at_any_time_without_academic_penalty.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'I understand I can withdraw from the pilot at any time without academic penalty.', 'value': 'acknowledged'}</t>
+          <t>I understand I can withdraw from the pilot at any time without academic penalty.</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand_that_this_pilot_does_not_change_the_existing_academic_integrity_policies_of_the_institution.',_'value':_'agreed'}</t>
+          <t>i_understand_that_this_pilot_does_not_change_the_existing_academic_integrity_policies_of_the_institution.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'I understand that this pilot does not change the existing academic integrity policies of the institution.', 'value': 'agreed'}</t>
+          <t>I understand that this pilot does not change the existing academic integrity policies of the institution.</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'i_confirm_my_participation_and_agreement_to_the_terms_above.',_'value':_'signed'}</t>
+          <t>i_confirm_my_participation_and_agreement_to_the_terms_above.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'I confirm my participation and agreement to the terms above.', 'value': 'signed'}</t>
+          <t>I confirm my participation and agreement to the terms above.</t>
         </is>
       </c>
     </row>
